--- a/EXCEL/Data/Figur_7+8_tabel_6/Figur_7+8.xlsx
+++ b/EXCEL/Data/Figur_7+8_tabel_6/Figur_7+8.xlsx
@@ -262,7 +262,7 @@
     <t>Datasæt 02 2016</t>
   </si>
   <si>
-    <t>Kørsel 15.4.2026 09.18.55</t>
+    <t>Kørsel 15.4.2026 09.26.06</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
